--- a/data_processing/assumptions_and_estimates/rough_cba_calculation.xlsx
+++ b/data_processing/assumptions_and_estimates/rough_cba_calculation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/ssp_uganda_data/data_processing/assumptions_and_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/data_processing/assumptions_and_estimates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CBD364-2987-624E-A6A6-BBCA093E8933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DBD191-6658-3A4D-A0AF-C6910B0F1411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5260" yWindow="4660" windowWidth="26040" windowHeight="14940" xr2:uid="{0C6EE969-DED8-EC42-8D7B-59B9297EB84D}"/>
+    <workbookView xWindow="-51200" yWindow="-7140" windowWidth="36040" windowHeight="28180" xr2:uid="{0C6EE969-DED8-EC42-8D7B-59B9297EB84D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -120,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -147,6 +147,12 @@
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -223,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -233,12 +239,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -260,9 +260,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -270,20 +288,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,16 +628,16 @@
   <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="10.83203125" style="7"/>
     <col min="2" max="2" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="6" customWidth="1"/>
     <col min="7" max="7" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="2.6640625" style="6" customWidth="1"/>
     <col min="12" max="12" width="17.83203125" customWidth="1"/>
     <col min="13" max="14" width="16.33203125" customWidth="1"/>
     <col min="15" max="15" width="4.6640625" customWidth="1"/>
@@ -640,71 +647,71 @@
     <col min="20" max="20" width="15.33203125" style="3" customWidth="1"/>
     <col min="21" max="21" width="16.5" style="3" customWidth="1"/>
     <col min="22" max="22" width="14.5" style="3" customWidth="1"/>
-    <col min="23" max="23" width="14.5" style="23" customWidth="1"/>
+    <col min="23" max="23" width="14.5" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="12" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="T1" s="21" t="s">
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="T1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="17" t="s">
+      <c r="F2" s="23"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="18" t="s">
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -719,90 +726,90 @@
       <c r="E3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="11" t="s">
+      <c r="J3" s="12"/>
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11" t="s">
+      <c r="O3" s="9"/>
+      <c r="P3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="T3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="U3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="V3" s="22" t="s">
+      <c r="V3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="22" t="s">
+      <c r="W3" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>0</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="A4" s="6">
+        <v>0</v>
+      </c>
+      <c r="B4" s="24">
+        <v>0.96032399999999996</v>
+      </c>
+      <c r="C4" s="24">
+        <v>2.3886999999999999E-2</v>
+      </c>
+      <c r="D4" s="24">
+        <v>1.1962E-2</v>
+      </c>
+      <c r="E4" s="6">
         <f>1-SUM(B4:D4)</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="F4" s="8">
+        <v>3.8270000000000248E-3</v>
+      </c>
+      <c r="F4" s="6">
         <v>1000000</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="6">
         <v>4</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6">
         <v>9</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="6">
         <v>5</v>
       </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="11"/>
       <c r="K4" s="2">
         <v>0</v>
       </c>
       <c r="L4">
         <f>MAX(B4-B5, 0)</f>
-        <v>0</v>
+        <v>2.7544999999999931E-2</v>
       </c>
       <c r="M4">
         <f>MAX(C4-C5, 0)</f>
@@ -814,11 +821,11 @@
       </c>
       <c r="P4">
         <f>MIN(L4,N15)</f>
-        <v>0</v>
+        <v>9.5839999999999988E-3</v>
       </c>
       <c r="Q4">
         <f>MIN(L4-P4,M15)</f>
-        <v>0</v>
+        <v>1.4894000000000004E-2</v>
       </c>
       <c r="R4">
         <f>MIN(N4,M15-Q4)</f>
@@ -826,131 +833,131 @@
       </c>
       <c r="T4" s="3">
         <f>$F4*G4*P4</f>
-        <v>0</v>
+        <v>38335.999999999993</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" ref="U4:V4" si="0">$F4*H4*Q4</f>
-        <v>0</v>
+        <v>134046.00000000003</v>
       </c>
       <c r="V4" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W4" s="23">
+      <c r="W4" s="16">
         <f>SUM(T4:V4)</f>
-        <v>0</v>
+        <v>172382.00000000003</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="B5" s="24">
+        <v>0.93277900000000002</v>
+      </c>
+      <c r="C5" s="24">
+        <v>3.8781000000000003E-2</v>
+      </c>
+      <c r="D5" s="24">
+        <v>2.1545999999999999E-2</v>
+      </c>
+      <c r="E5" s="6">
         <f t="shared" ref="E5:E11" si="1">1-SUM(B5:D5)</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="F5" s="8">
+        <v>6.8940000000000667E-3</v>
+      </c>
+      <c r="F5" s="6">
         <v>1100000</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="6">
         <v>4</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="6">
         <v>9</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="6">
         <v>5</v>
       </c>
-      <c r="J5" s="13"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:N10" si="2">MAX(B5-B6, 0)</f>
-        <v>2.0000000000000018E-2</v>
+        <f>MAX(B5-B6, 0)</f>
+        <v>3.1764000000000014E-2</v>
       </c>
       <c r="M5">
-        <f t="shared" si="2"/>
+        <f>MAX(C5-C6, 0)</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L5:N10" si="2">MAX(D5-D6, 0)</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f t="shared" ref="P5:P10" si="3">MIN(L5,N16)</f>
-        <v>2.0000000000000004E-2</v>
+        <f>MIN(L5,N16)</f>
+        <v>1.0886000000000003E-2</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q10" si="4">MIN(L5-P5,M16)</f>
-        <v>0</v>
+        <f t="shared" ref="Q5:Q10" si="3">MIN(L5-P5,M16)</f>
+        <v>1.7392999999999999E-2</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R10" si="5">MIN(N5,M16-Q5)</f>
+        <f t="shared" ref="R5:R10" si="4">MIN(N5,M16-Q5)</f>
         <v>0</v>
       </c>
       <c r="T5" s="3">
         <f>$F5*G5*P5</f>
-        <v>88000.000000000015</v>
+        <v>47898.400000000016</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" ref="U5:U10" si="6">$F5*H5*Q5</f>
-        <v>0</v>
+        <f t="shared" ref="U5:U10" si="5">$F5*H5*Q5</f>
+        <v>172190.69999999998</v>
       </c>
       <c r="V5" s="3">
-        <f t="shared" ref="V5:V10" si="7">$F5*I5*R5</f>
-        <v>0</v>
-      </c>
-      <c r="W5" s="23">
-        <f t="shared" ref="W5:W10" si="8">SUM(T5:V5)</f>
-        <v>88000.000000000015</v>
+        <f t="shared" ref="V5:V10" si="6">$F5*I5*R5</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="16">
+        <f t="shared" ref="W5:W10" si="7">SUM(T5:V5)</f>
+        <v>220089.1</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
-        <v>0.88</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C6" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D6" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E6" s="6">
         <f>1-SUM(B6:D6)</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="F6" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F6" s="6">
         <v>1200000</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>4</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>9</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="6">
         <v>5</v>
       </c>
-      <c r="J6" s="13"/>
+      <c r="J6" s="11"/>
       <c r="K6" s="2">
         <v>2</v>
       </c>
       <c r="L6">
         <f t="shared" si="2"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
@@ -961,70 +968,70 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <f t="shared" si="3"/>
-        <v>1.999999999999999E-2</v>
+        <f>MIN(L6,N17)</f>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f>MIN(L6-P6,M17)</f>
-        <v>2.7755575615628914E-17</v>
+        <v>0</v>
       </c>
       <c r="R6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <f t="shared" ref="T6:T10" si="8">$F6*G6*P6</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T6" s="3">
-        <f t="shared" ref="T5:T10" si="9">$F6*G6*P6</f>
-        <v>95999.999999999956</v>
-      </c>
-      <c r="U6" s="3">
+      <c r="V6" s="3">
         <f t="shared" si="6"/>
-        <v>2.9976021664879227E-10</v>
-      </c>
-      <c r="V6" s="3">
+        <v>0</v>
+      </c>
+      <c r="W6" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W6" s="23">
-        <f t="shared" si="8"/>
-        <v>96000.000000000262</v>
-      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="8">
-        <v>0.86</v>
-      </c>
-      <c r="C7" s="8">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="B7" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C7" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D7" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E7" s="6">
         <f t="shared" si="1"/>
-        <v>1.5000000000000013E-2</v>
-      </c>
-      <c r="F7" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F7" s="6">
         <v>1350000</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>4</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="6">
         <v>9</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>5</v>
       </c>
-      <c r="J7" s="13"/>
+      <c r="J7" s="11"/>
       <c r="K7" s="2">
         <v>3</v>
       </c>
       <c r="L7">
         <f t="shared" si="2"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <f t="shared" si="2"/>
@@ -1035,70 +1042,70 @@
         <v>0</v>
       </c>
       <c r="P7">
+        <f t="shared" ref="P5:P10" si="9">MIN(L7,N18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="3"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R7">
+      <c r="T7" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T7" s="3">
-        <f t="shared" si="9"/>
-        <v>108000.0000000001</v>
-      </c>
-      <c r="U7" s="3">
+      <c r="V7" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W7" s="23">
-        <f t="shared" si="8"/>
-        <v>108000.0000000001</v>
-      </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0.01</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B8" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C8" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D8" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E8" s="6">
         <f t="shared" si="1"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="F8" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F8" s="6">
         <v>1500000</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>4</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>9</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="6">
         <v>5</v>
       </c>
-      <c r="J8" s="13"/>
+      <c r="J8" s="11"/>
       <c r="K8" s="2">
         <v>4</v>
       </c>
       <c r="L8">
         <f t="shared" si="2"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
@@ -1109,70 +1116,70 @@
         <v>0</v>
       </c>
       <c r="P8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="3"/>
-        <v>1.999999999999999E-2</v>
-      </c>
-      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="4"/>
-        <v>2.7755575615628914E-17</v>
-      </c>
-      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T8" s="3">
-        <f t="shared" si="9"/>
-        <v>119999.99999999994</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <f t="shared" si="6"/>
-        <v>3.7470027081099033E-10</v>
-      </c>
-      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W8" s="23">
-        <f t="shared" si="8"/>
-        <v>120000.00000000032</v>
-      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B9" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C9" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D9" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E9" s="6">
         <f t="shared" si="1"/>
-        <v>5.0000000000000044E-3</v>
-      </c>
-      <c r="F9" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F9" s="6">
         <v>1720000</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>4</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <v>9</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="6">
         <v>5</v>
       </c>
-      <c r="J9" s="13"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="2">
         <v>5</v>
       </c>
       <c r="L9">
         <f t="shared" si="2"/>
-        <v>1.9999999999999907E-2</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
@@ -1183,70 +1190,70 @@
         <v>0</v>
       </c>
       <c r="P9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <f t="shared" si="4"/>
-        <v>1.0000000000000002E-2</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U9" s="3">
         <f>$F9*H9*Q9</f>
-        <v>154800.00000000003</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W9" s="23">
-        <f t="shared" si="8"/>
-        <v>154800.00000000003</v>
-      </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C10" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D10" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E10" s="6">
         <f t="shared" si="1"/>
-        <v>1.4999999999999902E-2</v>
-      </c>
-      <c r="F10" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F10" s="6">
         <v>1820000</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>4</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <v>9</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="6">
         <v>5</v>
       </c>
-      <c r="J10" s="13"/>
+      <c r="J10" s="11"/>
       <c r="K10" s="2">
         <v>6</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
@@ -1257,197 +1264,197 @@
         <v>0</v>
       </c>
       <c r="P10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <f t="shared" si="4"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T10" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <f t="shared" si="6"/>
-        <v>245700</v>
-      </c>
-      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="16">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="W10" s="23">
-        <f t="shared" si="8"/>
-        <v>245700</v>
-      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="8">
-        <v>0.78</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="24">
+        <v>0.90101500000000001</v>
+      </c>
+      <c r="C11" s="24">
+        <v>5.6174000000000002E-2</v>
+      </c>
+      <c r="D11" s="24">
+        <v>3.2432000000000002E-2</v>
+      </c>
+      <c r="E11" s="6">
         <f t="shared" si="1"/>
-        <v>1.9999999999999907E-2</v>
-      </c>
-      <c r="F11" s="8">
+        <v>1.0378999999999916E-2</v>
+      </c>
+      <c r="F11" s="6">
         <v>1900000</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>4</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>9</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <v>5</v>
       </c>
-      <c r="J11" s="13"/>
+      <c r="J11" s="11"/>
       <c r="K11" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="J12" s="13"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="J13" s="13"/>
+      <c r="J13" s="11"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="J14" s="13"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="11" t="s">
+      <c r="J14" s="11"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="J15" s="13"/>
+      <c r="J15" s="11"/>
       <c r="L15">
         <f>MAX(B5-B4, 0)</f>
         <v>0</v>
       </c>
       <c r="M15">
         <f>MAX(C5-C4, 0)</f>
-        <v>0</v>
+        <v>1.4894000000000004E-2</v>
       </c>
       <c r="N15">
-        <f>MAX(D5-D4, 0)</f>
-        <v>0</v>
+        <f t="shared" ref="L15:N21" si="10">MAX(D5-D4, 0)</f>
+        <v>9.5839999999999988E-3</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="J16" s="13"/>
+      <c r="J16" s="11"/>
       <c r="L16">
-        <f>MAX(B6-B5, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>MAX(C6-C5, 0)</f>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1.7392999999999999E-2</v>
       </c>
       <c r="N16">
-        <f>MAX(D6-D5, 0)</f>
-        <v>2.0000000000000004E-2</v>
+        <f t="shared" si="10"/>
+        <v>1.0886000000000003E-2</v>
       </c>
     </row>
     <row r="17" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J17" s="13"/>
+      <c r="J17" s="11"/>
       <c r="L17">
-        <f>MAX(B7-B6, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f>MAX(C7-C6, 0)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="N17">
-        <f>MAX(D7-D6, 0)</f>
-        <v>1.999999999999999E-2</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J18" s="13"/>
+      <c r="J18" s="11"/>
       <c r="L18">
-        <f>MAX(B8-B7, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M18">
-        <f>MAX(C8-C7, 0)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="N18">
-        <f>MAX(D8-D7, 0)</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J19" s="13"/>
+      <c r="J19" s="11"/>
       <c r="L19">
-        <f>MAX(B9-B8, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M19">
-        <f>MAX(C9-C8, 0)</f>
-        <v>4.9999999999999992E-3</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="N19">
-        <f>MAX(D9-D8, 0)</f>
-        <v>1.999999999999999E-2</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J20" s="13"/>
+      <c r="J20" s="11"/>
       <c r="L20">
-        <f>MAX(B10-B9, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M20">
-        <f>MAX(C10-C9, 0)</f>
-        <v>1.0000000000000002E-2</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="N20">
-        <f>MAX(D10-D9, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J21" s="13"/>
+      <c r="J21" s="11"/>
       <c r="L21">
-        <f>MAX(B11-B10, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M21">
-        <f>MAX(C11-C10, 0)</f>
-        <v>1.4999999999999999E-2</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="N21">
-        <f>MAX(D11-D10, 0)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J22" s="13"/>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" spans="10:14" x14ac:dyDescent="0.2">
-      <c r="J23" s="13"/>
+      <c r="J23" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="7">
